--- a/output/pdf_financials_xlsx/DIR.UN.xlsx
+++ b/output/pdf_financials_xlsx/DIR.UN.xlsx
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>-2.326</v>
+        <v>0.042</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>-1.705</v>
@@ -33730,7 +33730,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DIR.UN.xlsx
+++ b/output/pdf_financials_xlsx/DIR.UN.xlsx
@@ -33572,7 +33572,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E339" s="5" t="n">
         <v>-20.873</v>
       </c>
@@ -34534,7 +34538,11 @@
           <t>Transaction costs included in net income (loss) 7</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E351" s="5" t="n">
         <v>11.528</v>
       </c>
